--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.9939863206805</v>
+        <v>6.011522777110581</v>
       </c>
       <c r="D2" t="n">
-        <v>42.66505942101847</v>
+        <v>6.933072155915501</v>
       </c>
       <c r="E2" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F2" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.6242387902277</v>
+        <v>1.726438803412001</v>
       </c>
       <c r="D3" t="n">
-        <v>11.42940494558242</v>
+        <v>1.857278303657143</v>
       </c>
       <c r="E3" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F3" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.96379418642734</v>
+        <v>10.88161655529444</v>
       </c>
       <c r="D4" t="n">
-        <v>79.08433277788058</v>
+        <v>12.85120407640559</v>
       </c>
       <c r="E4" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F4" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.14177346495913</v>
+        <v>8.635538188055859</v>
       </c>
       <c r="D5" t="n">
-        <v>60.94534276509258</v>
+        <v>9.903618199327545</v>
       </c>
       <c r="E5" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F5" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.13759939440093</v>
+        <v>8.959859901590152</v>
       </c>
       <c r="D6" t="n">
-        <v>76.63010286724604</v>
+        <v>12.45239171592748</v>
       </c>
       <c r="E6" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F6" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>68.28311825659507</v>
+        <v>11.0960067166967</v>
       </c>
       <c r="D7" t="n">
-        <v>71.79927498355954</v>
+        <v>11.66738218482843</v>
       </c>
       <c r="E7" t="n">
-        <v>19.85298217648441</v>
+        <v>3.226109603678716</v>
       </c>
       <c r="F7" t="n">
-        <v>23.76889267425216</v>
+        <v>3.862445059565976</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
